--- a/docs/最新版/02_管理シート/MVP実行計画.xlsx
+++ b/docs/最新版/02_管理シート/MVP実行計画.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,8 +49,12 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,17 +73,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8740C"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -123,16 +117,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -517,7 +509,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01 リリースに向けた実行管理シート。全てのシートは「誰が・いつまでに・何をするか」で書かれています。</t>
+          <t>2026-05-01 リリースに向けた実行管理シート。全シートは「誰が・いつまでに・何をするか」で書かれています。</t>
         </is>
       </c>
     </row>
@@ -602,7 +594,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>10社それぞれの連絡・契約・撮影・成果の進捗管理</t>
+          <t>10社それぞれの連絡・契約・撮影・送客の進捗管理</t>
         </is>
       </c>
     </row>
@@ -636,7 +628,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>リリース後12ヶ月のKPI目標と実績記録欄</t>
+          <t>リリース後12ヶ月のKPI目標と実績記録欄 (全員同一料金)</t>
         </is>
       </c>
     </row>
@@ -780,7 +772,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>本番用 .env 設定 (NextAuth, Supabase, Stripe)</t>
+          <t>本番用 .env 設定 (NextAuth, Supabase)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -916,7 +908,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>イベント: diagnosis_start, event_booking</t>
+          <t>lead_source を追跡可能に</t>
         </is>
       </c>
     </row>
@@ -953,7 +945,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>signup, contact, event booking</t>
+          <t>signup/contact/event booking</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1130,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>料金プラン_MVP版.md 添付</t>
+          <t>料金プラン_MVP版.docx 添付 (全員同一料金)</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1142,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>工務店10社と料金プラン最終合意</t>
+          <t>工務店10社と料金プラン最終合意 (¥50,000/件)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1212,7 +1204,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>想定Q&amp;A 20問</t>
+          <t>想定Q&amp;A 20問、10社優遇=AI診断優先送客のみ</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1241,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>お問い合わせ → 24h以内返信ルール</t>
+          <t>24h以内返信ルール</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1278,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>見学会予約 ¥50,000 税込・振込先</t>
+          <t>見学会予約 ¥50,000 税別・振込先</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1315,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>弥生会計 / freee どちらで管理するか決定</t>
+          <t>freee で管理</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1401,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>SNS リリース告知予約投稿 (X, Instagram, Threads)</t>
+          <t>SNS リリース告知予約投稿</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1434,7 +1426,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>5/1 AM 9:00 に自動投稿</t>
+          <t>X/Instagram/Threads</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1463,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Vercel プレビュー → プロダクション昇格の手順確認</t>
+          <t>Vercel preview → production</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1649,7 +1641,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>先週比+10%以上なら維持、-10%なら原因分析</t>
+          <t>先週比+10%以上なら維持</t>
         </is>
       </c>
     </row>
@@ -1720,39 +1712,39 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>火</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>YouTube 来週の動画スクリプト確認</t>
+          <t>問合せフォームから来た連絡への対応</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>代表</t>
+          <t>営業</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>毎週</t>
+          <t>毎日</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>24h以内に全件返信</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1762,22 +1754,22 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>問合せフォームから来た連絡への対応</t>
+          <t>YouTube 新着動画の公開 + ぺいほーむ掲載</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>営業</t>
+          <t>代表</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>毎日</t>
+          <t>毎週水</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>24h以内に全件返信</t>
+          <t>YouTube公開から1時間以内に掲載</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1781,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>YouTube 新着動画の公開 + ぺいほーむ掲載</t>
+          <t>SNS: 動画公開の拡散 (X, Instagram, Threads)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1809,39 +1801,39 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>YouTube公開から1時間以内に掲載</t>
+          <t>全プラットフォーム投稿で✓</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>SNS: 動画公開の拡散 (X, Instagram, Threads)</t>
+          <t>見学会予約の工務店確認 (通知届いたか)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>代表</t>
+          <t>営業</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>毎週水</t>
+          <t>毎週</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>全プラットフォーム投稿で✓</t>
+          <t>全件確認で✓</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1845,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>見学会予約の工務店確認 (通知届いたか)</t>
+          <t>工務店10社のうち1社と電話フォローアップ</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1873,7 +1865,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>全件確認で✓</t>
+          <t>週1社 × 10週 = 全社巡回</t>
         </is>
       </c>
     </row>
@@ -1885,17 +1877,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>工務店10社のうち1社と電話フォローアップ</t>
+          <t>週次 KPI を経理・代表に共有</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>営業</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1905,103 +1897,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>週1社 × 10週 = 全社巡回</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>週次 KPI を経理・代表に共有</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>毎週</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>スプレッドシート更新</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>深刻な障害発生時のオンコール</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>エンジニア</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>随時</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>ブログ/Note の記事執筆 (月2本目標)</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>代表</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>隔週</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>−</t>
+          <t>月次売上ペースも確認</t>
         </is>
       </c>
     </row>
@@ -2020,7 +1916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2042,7 +1938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>いつ何を復活させるか。エンジニアの実装計画と同期</t>
+          <t>いつ何を復活させるか</t>
         </is>
       </c>
     </row>
@@ -2096,7 +1992,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>運用のみ</t>
+          <t>運用のみ (MVP 17画面)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2116,7 +2012,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>見学会予約¥50,000 + 3% を運用開始</t>
+          <t>見学会予約 ¥50,000/件 のみ運用開始</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2234,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>月額掲載 ¥30,000 開始</t>
+          <t>月額掲載 ¥30,000/¥80,000 開始</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2271,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>月額掲載 ¥30,000 開始</t>
+          <t>−</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2362,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>エリア別ページ</t>
+          <t>成果報酬トラッキング実装</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>/area</t>
+          <t>lead_source tracking</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -2481,12 +2377,12 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>★成果報酬 3% 開始 (無料相談/AI診断/会員成約)</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2399,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>工務店 建売/土地CMS</t>
+          <t>エリア別ページ</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/builder/sale-homes, /lands</t>
+          <t>/area</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -2518,7 +2414,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -2540,12 +2436,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>工務店比較</t>
+          <t>工務店 建売/土地CMS</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>/builders/compare</t>
+          <t>/dashboard/builder/sale-homes, /lands</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -2555,7 +2451,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -2567,22 +2463,22 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026/12/01〜2027/02/28</t>
+          <t>2026/09/01〜11/30</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>匿名AI仲介質問</t>
+          <t>工務店比較</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>/mypage/questions, /dashboard/builder/questions</t>
+          <t>/builders/compare</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -2592,12 +2488,12 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>SaaS ¥50,000/月 開始</t>
+          <t>−</t>
         </is>
       </c>
     </row>
@@ -2614,12 +2510,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>ウェビナー</t>
+          <t>匿名AI仲介質問</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>/webinar, /webinar/[id]</t>
+          <t>/mypage/questions</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2629,12 +2525,12 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>SaaS に含む</t>
+          <t>SaaS ¥50,000/¥150,000 開始</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2547,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>マガジン</t>
+          <t>ウェビナー</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>/magazine</t>
+          <t>/webinar, /webinar/[id]</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -2666,7 +2562,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -2688,12 +2584,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>インタビュー</t>
+          <t>マガジン</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>/interview, /interview/[id]</t>
+          <t>/magazine</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2725,12 +2621,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Stripe決済 + 請求自動化</t>
+          <t>インタビュー</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>内部実装</t>
+          <t>/interview, /interview/[id]</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -2740,12 +2636,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>全プランに必須</t>
+          <t>SaaS に含む</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2658,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>管理画面 全CMS</t>
+          <t>Stripe決済 + 請求自動化</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>/admin/* 全て</t>
+          <t>内部実装</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2777,49 +2673,86 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>全プランに必須</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/01〜2027/02/28</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>管理画面 全CMS</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>/admin/* 全て</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>エンジニア</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>2027/03〜</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>全国工務店追加</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>builders-data 拡張</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>営業+エンジニア</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>2027-03-31</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>提携料は正規価格</t>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>有料広告投資開始</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2850,8 +2783,9 @@
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2864,7 +2798,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>契約・撮影・成果の進捗を社単位で追跡</t>
+          <t>全員同一料金。10社は AI診断の優先送客のみ差別化</t>
         </is>
       </c>
     </row>
@@ -2911,15 +2845,20 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>累計成果報酬</t>
+          <t>累計撮影本数</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>累計成約数</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>最終連絡日</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>次回アクション</t>
         </is>
@@ -2957,8 +2896,11 @@
       <c r="I5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -2992,8 +2934,11 @@
       <c r="I6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -3027,8 +2972,11 @@
       <c r="I7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -3062,8 +3010,11 @@
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="n">
@@ -3097,8 +3048,11 @@
       <c r="I9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -3132,8 +3086,11 @@
       <c r="I10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="n">
@@ -3167,8 +3124,11 @@
       <c r="I11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -3202,8 +3162,11 @@
       <c r="I12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="n">
@@ -3237,8 +3200,11 @@
       <c r="I13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -3272,13 +3238,16 @@
       <c r="I14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3469,7 +3438,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Turnstile (bot対策) 有効</t>
+          <t>Turnstile 有効 (signup/contact/event)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -3538,7 +3507,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>GA4 計測タグ動作確認</t>
+          <t>GA4 + lead_source tracking 動作確認</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -3653,7 +3622,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>AI診断フロー完走確認</t>
+          <t>AI診断フロー完走確認 (10社優先表示)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -3837,7 +3806,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>10社と料金プラン書面締結</t>
+          <t>10社と料金プラン書面締結 (¥50,000/件)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -4138,29 +4107,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⑥ 月次 KPI トラッキング</t>
+          <t>⑥ 月次 KPI トラッキング (全員同一料金)</t>
         </is>
       </c>
     </row>
@@ -4171,73 +4140,10 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="5" t="inlineStr"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-    </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>指標</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -4307,592 +4213,484 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>月間UU</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr"/>
-      <c r="C5" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>7500</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>12500</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>17500</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>25000</v>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>30000</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>33000</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>36000</v>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>40000</v>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>目標 UU</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>見学会予約 件数 (目標)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>実績 UU</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実績</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>AI診断 完了数</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr"/>
-      <c r="C8" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>300</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>400</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>600</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>800</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>1400</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>1500</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>撮影プラン 本数</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>目標</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr"/>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr"/>
-      <c r="J9" s="8" t="inlineStr"/>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実績</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr"/>
-      <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr"/>
-      <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="9" t="inlineStr"/>
-      <c r="I10" s="9" t="inlineStr"/>
-      <c r="J10" s="9" t="inlineStr"/>
-      <c r="K10" s="9" t="inlineStr"/>
-      <c r="L10" s="9" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr"/>
-      <c r="N10" s="9" t="inlineStr"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>月額掲載 社数</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>見学会予約 数</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr"/>
-      <c r="C11" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>70</v>
-      </c>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実績</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr"/>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr"/>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>目標</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="8" t="inlineStr"/>
-      <c r="M12" s="8" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>成果報酬 成約件数</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr"/>
-      <c r="C13" s="9" t="inlineStr"/>
-      <c r="D13" s="9" t="inlineStr"/>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="9" t="inlineStr"/>
-      <c r="G13" s="9" t="inlineStr"/>
-      <c r="H13" s="9" t="inlineStr"/>
-      <c r="I13" s="9" t="inlineStr"/>
-      <c r="J13" s="9" t="inlineStr"/>
-      <c r="K13" s="9" t="inlineStr"/>
-      <c r="L13" s="9" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr"/>
-      <c r="N13" s="9" t="inlineStr"/>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実績</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>撮影プラン 本数</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr"/>
-      <c r="C14" s="7" t="n">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>SaaS 総社数</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" s="7" t="n">
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K14" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="M14" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="N14" s="7" t="n">
+      <c r="M14" s="5" t="n">
         <v>9</v>
       </c>
+      <c r="N14" s="5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>目標</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr"/>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="8" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr"/>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
-      <c r="M15" s="8" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実績</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="9" t="inlineStr"/>
-      <c r="D16" s="9" t="inlineStr"/>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="9" t="inlineStr"/>
-      <c r="G16" s="9" t="inlineStr"/>
-      <c r="H16" s="9" t="inlineStr"/>
-      <c r="I16" s="9" t="inlineStr"/>
-      <c r="J16" s="9" t="inlineStr"/>
-      <c r="K16" s="9" t="inlineStr"/>
-      <c r="L16" s="9" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr"/>
-      <c r="N16" s="9" t="inlineStr"/>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>月次売上 (円)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>¥500,000</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>¥750,000</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>¥1,150,000</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>¥1,550,000</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>¥2,940,000</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>¥4,150,000</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>¥4,640,000</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>¥5,950,000</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>¥6,510,000</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>¥7,940,000</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>¥8,500,000</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>¥9,960,000</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>月額掲載 社数</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr"/>
-      <c r="C17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="L17" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>目標</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr"/>
-      <c r="C18" s="8" t="inlineStr"/>
-      <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
-      <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="8" t="inlineStr"/>
-      <c r="J18" s="8" t="inlineStr"/>
-      <c r="K18" s="8" t="inlineStr"/>
-      <c r="L18" s="8" t="inlineStr"/>
-      <c r="M18" s="8" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr"/>
-      <c r="C19" s="9" t="inlineStr"/>
-      <c r="D19" s="9" t="inlineStr"/>
-      <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="9" t="inlineStr"/>
-      <c r="G19" s="9" t="inlineStr"/>
-      <c r="H19" s="9" t="inlineStr"/>
-      <c r="I19" s="9" t="inlineStr"/>
-      <c r="J19" s="9" t="inlineStr"/>
-      <c r="K19" s="9" t="inlineStr"/>
-      <c r="L19" s="9" t="inlineStr"/>
-      <c r="M19" s="9" t="inlineStr"/>
-      <c r="N19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>SaaS 社数</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr"/>
-      <c r="C20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M20" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>目標</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr"/>
-      <c r="C21" s="8" t="inlineStr"/>
-      <c r="D21" s="8" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr"/>
-      <c r="J21" s="8" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="8" t="inlineStr"/>
-      <c r="M21" s="8" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr"/>
-      <c r="C22" s="9" t="inlineStr"/>
-      <c r="D22" s="9" t="inlineStr"/>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="9" t="inlineStr"/>
-      <c r="I22" s="9" t="inlineStr"/>
-      <c r="J22" s="9" t="inlineStr"/>
-      <c r="K22" s="9" t="inlineStr"/>
-      <c r="L22" s="9" t="inlineStr"/>
-      <c r="M22" s="9" t="inlineStr"/>
-      <c r="N22" s="9" t="inlineStr"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>月次売上 (円)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr"/>
-      <c r="C23" s="7" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>250000</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>400000</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>550000</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>750000</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>950000</v>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="J23" s="7" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="L23" s="7" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="M23" s="7" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>2350000</v>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>目標</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr"/>
-      <c r="C24" s="8" t="inlineStr"/>
-      <c r="D24" s="8" t="inlineStr"/>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="8" t="inlineStr"/>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="8" t="inlineStr"/>
-      <c r="J24" s="8" t="inlineStr"/>
-      <c r="K24" s="8" t="inlineStr"/>
-      <c r="L24" s="8" t="inlineStr"/>
-      <c r="M24" s="8" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr"/>
-      <c r="C25" s="9" t="inlineStr"/>
-      <c r="D25" s="9" t="inlineStr"/>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="9" t="inlineStr"/>
-      <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="9" t="inlineStr"/>
-      <c r="I25" s="9" t="inlineStr"/>
-      <c r="J25" s="9" t="inlineStr"/>
-      <c r="K25" s="9" t="inlineStr"/>
-      <c r="L25" s="9" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr"/>
-      <c r="N25" s="9" t="inlineStr"/>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実績</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr"/>
+      <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5742,7 +5540,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>B2Bサービス概要 (大幅リニューアル)</t>
+          <t>B2Bサービス概要</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6030,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>/admin/security, /activity, /system, /notifications, /data</t>
+          <t>/admin/security/activity/system/notifications/data</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
